--- a/transport_data.xlsx
+++ b/transport_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Source</t>
   </si>
@@ -25,10 +25,7 @@
     <t>Amount Transported (tonnes)</t>
   </si>
   <si>
-    <t>Colwick Industrial Estate</t>
-  </si>
-  <si>
-    <t>East London Biogas</t>
+    <t>Ellesmere Port Biodiesel Plant</t>
   </si>
   <si>
     <t>Factory Road AD</t>
@@ -37,31 +34,43 @@
     <t>Foxhills Industrial Estate</t>
   </si>
   <si>
-    <t>Haznortra Farm AD</t>
+    <t>Frog Island AD</t>
+  </si>
+  <si>
+    <t>Garth Road AD</t>
+  </si>
+  <si>
+    <t>GENeco Food Waste Recycling Plant</t>
   </si>
   <si>
     <t>Kemsley Paper Mill</t>
   </si>
   <si>
+    <t>Langage Farm</t>
+  </si>
+  <si>
+    <t>Lostock Works</t>
+  </si>
+  <si>
     <t>Manor Farm (Beal)</t>
   </si>
   <si>
-    <t>Manor Farm (Newton-on-trent)</t>
+    <t>Mauri Products</t>
+  </si>
+  <si>
+    <t>North Moor Farm</t>
+  </si>
+  <si>
+    <t>Pinguin Foods</t>
+  </si>
+  <si>
+    <t>ReFood Widnes</t>
   </si>
   <si>
     <t>Smeathalls Farm</t>
   </si>
   <si>
-    <t>South Wales AD Facility</t>
-  </si>
-  <si>
-    <t>Spalford AD</t>
-  </si>
-  <si>
     <t>Sutton Courtenay AD</t>
-  </si>
-  <si>
-    <t>Sutton Grange AD</t>
   </si>
   <si>
     <t>Teeside Green Energy Plant</t>
@@ -425,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -444,10 +453,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>14285.714</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -455,10 +464,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="C3">
-        <v>14285.714</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -466,10 +475,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>278</v>
       </c>
       <c r="C4">
-        <v>13000</v>
+        <v>18615</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -477,10 +486,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>14285.714</v>
+        <v>71428.571</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -488,10 +497,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1285.7143</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -499,10 +508,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C7">
-        <v>14285.714</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -510,10 +519,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C8">
-        <v>10675</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -521,10 +530,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="C9">
-        <v>13000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -532,10 +541,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="C10">
-        <v>3610.7143</v>
+        <v>71428.571</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -543,10 +552,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C11">
-        <v>14285.714</v>
+        <v>10675</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -554,10 +563,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C12">
-        <v>14285.714</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -565,10 +574,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C13">
-        <v>14285.714</v>
+        <v>3995.7143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -576,10 +585,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="C14">
-        <v>1285.7143</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -587,10 +596,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C15">
-        <v>14285.714</v>
+        <v>71428.571</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -598,10 +607,43 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C16">
-        <v>14285.714</v>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>70</v>
+      </c>
+      <c r="C17">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>71428.571</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>48</v>
+      </c>
+      <c r="C19">
+        <v>11428.571</v>
       </c>
     </row>
   </sheetData>

--- a/transport_data.xlsx
+++ b/transport_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
   <si>
     <t>Source</t>
   </si>
@@ -25,58 +25,301 @@
     <t>Amount Transported (tonnes)</t>
   </si>
   <si>
-    <t>Ellesmere Port Biodiesel Plant</t>
-  </si>
-  <si>
-    <t>Factory Road AD</t>
-  </si>
-  <si>
-    <t>Foxhills Industrial Estate</t>
-  </si>
-  <si>
-    <t>Frog Island AD</t>
-  </si>
-  <si>
-    <t>Garth Road AD</t>
-  </si>
-  <si>
-    <t>GENeco Food Waste Recycling Plant</t>
-  </si>
-  <si>
-    <t>Kemsley Paper Mill</t>
-  </si>
-  <si>
-    <t>Langage Farm</t>
+    <t>Colwick Industrial Estate</t>
+  </si>
+  <si>
+    <t>Cumbernauld AD</t>
+  </si>
+  <si>
+    <t>Hemswell Cliff Industrial Estate</t>
+  </si>
+  <si>
+    <t>Local Generation</t>
+  </si>
+  <si>
+    <t>London Sustainable Industries Park (ReFood)</t>
   </si>
   <si>
     <t>Lostock Works</t>
   </si>
   <si>
-    <t>Manor Farm (Beal)</t>
-  </si>
-  <si>
-    <t>Mauri Products</t>
-  </si>
-  <si>
-    <t>North Moor Farm</t>
-  </si>
-  <si>
-    <t>Pinguin Foods</t>
+    <t>Poplars Landfill AD</t>
+  </si>
+  <si>
+    <t>ReFood Doncaster AD</t>
   </si>
   <si>
     <t>ReFood Widnes</t>
   </si>
   <si>
-    <t>Smeathalls Farm</t>
-  </si>
-  <si>
-    <t>Sutton Courtenay AD</t>
+    <t>SS Agri AD Power Facility / Attleborough AD Plant</t>
+  </si>
+  <si>
+    <t>Stanley's Quarry</t>
   </si>
   <si>
     <t>Teeside Green Energy Plant</t>
   </si>
   <si>
-    <t>Willow Farm (Avonmouth)</t>
+    <t>Tully Quarry</t>
+  </si>
+  <si>
+    <t>Warrens Emerald Biogas</t>
+  </si>
+  <si>
+    <t>FIFE COUNCIL56.099604</t>
+  </si>
+  <si>
+    <t>SCOTTISH WATER55.926707</t>
+  </si>
+  <si>
+    <t>ANDREW COOK (CONTAINERS) LIMITED56.162618</t>
+  </si>
+  <si>
+    <t>FALKIRK COUNCIL ROADS SERVICES56.006112</t>
+  </si>
+  <si>
+    <t>M E C Recycling Ltd53.160691</t>
+  </si>
+  <si>
+    <t>Land Network ( Gainsborough ) Limited53.375045</t>
+  </si>
+  <si>
+    <t>New Earth Solutions ( West ) Limited52.787601</t>
+  </si>
+  <si>
+    <t>Royal Household Property Section51.501009</t>
+  </si>
+  <si>
+    <t>Seymour                  Thomas54.438541</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kew51.483651</t>
+  </si>
+  <si>
+    <t>P G &amp; H M Jackson53.356268</t>
+  </si>
+  <si>
+    <t>Bloomfield Composting Limited52.71334</t>
+  </si>
+  <si>
+    <t>Caton                    Andrew52.60374</t>
+  </si>
+  <si>
+    <t>The Royal Parks - Kensington Park51.50657834</t>
+  </si>
+  <si>
+    <t>The Royal Parks51.5286073</t>
+  </si>
+  <si>
+    <t>The Royal Parks - Greenwich Park51.473</t>
+  </si>
+  <si>
+    <t>Gorsefield Farm Ltd53.4324</t>
+  </si>
+  <si>
+    <t>Birmingham City Council52.38470077</t>
+  </si>
+  <si>
+    <t>Brinklow Quarry Limited52.41139</t>
+  </si>
+  <si>
+    <t>3 C Waste Ltd53.2428743</t>
+  </si>
+  <si>
+    <t>Eric Langton And Janet Langton53.38249</t>
+  </si>
+  <si>
+    <t>George Whittaker And Sons ( Knutsford ) Ltd53.26558</t>
+  </si>
+  <si>
+    <t>C E &amp; A Walley53.169504</t>
+  </si>
+  <si>
+    <t>C R J Services Ltd53.12439</t>
+  </si>
+  <si>
+    <t>Peterborough City Council52.59344</t>
+  </si>
+  <si>
+    <t>Veolia E S Cleanaway ( U K ) Ltd51.5559918</t>
+  </si>
+  <si>
+    <t>Grendon Recycling Limited52.6137405</t>
+  </si>
+  <si>
+    <t>Severn Trent Green Power (Hertfordshire) Limited51.7097132</t>
+  </si>
+  <si>
+    <t>The Greener Gardening Company (Kirkby) Limited53.47081</t>
+  </si>
+  <si>
+    <t>Hollybush Recycling Limited52.6573059</t>
+  </si>
+  <si>
+    <t>Highfield Environmental Limited54.61593</t>
+  </si>
+  <si>
+    <t>S.E.D. Services Limited53.5073</t>
+  </si>
+  <si>
+    <t>A Broster Limited53.46496</t>
+  </si>
+  <si>
+    <t>TJ Composting Services Limited51.72269825</t>
+  </si>
+  <si>
+    <t>SUEZ Recycling and Recovery UK Ltd 152.4614199</t>
+  </si>
+  <si>
+    <t>Material Change Limited52.69838</t>
+  </si>
+  <si>
+    <t>TJ Composting Services Limited51.4035273</t>
+  </si>
+  <si>
+    <t>SUEZ Recycling and Recovery UK Ltd 253.539242</t>
+  </si>
+  <si>
+    <t>SUEZ Recycling and Recovery UK Ltd 353.47682193</t>
+  </si>
+  <si>
+    <t>Ryman; Ryman52.65618</t>
+  </si>
+  <si>
+    <t>The Greener Gardening Company (Kirkby) Limited53.52721448</t>
+  </si>
+  <si>
+    <t>Berkswell Recycling Limited52.42737</t>
+  </si>
+  <si>
+    <t>Veolia ES Landfill Ltd52.6562266</t>
+  </si>
+  <si>
+    <t>Heyes; Heyes; Heyes53.48498</t>
+  </si>
+  <si>
+    <t>Thompson54.6731951</t>
+  </si>
+  <si>
+    <t>Riverside Bio Limited 51.39312</t>
+  </si>
+  <si>
+    <t>A &amp; E Thompson54.67941</t>
+  </si>
+  <si>
+    <t>A Broster Ltd53.46496</t>
+  </si>
+  <si>
+    <t>Andrew Cook56.16268</t>
+  </si>
+  <si>
+    <t>Brier Hills Recycling Limited53.57893</t>
+  </si>
+  <si>
+    <t>Down to Earth Recycling Ltd53.5009299</t>
+  </si>
+  <si>
+    <t>AB Waste Management t/a Bloomfield Composting52.71334</t>
+  </si>
+  <si>
+    <t>FCC Environment (UK) Ltd53.2428743</t>
+  </si>
+  <si>
+    <t>Forth Resource Management Limited - Braehead55.94862</t>
+  </si>
+  <si>
+    <t>Freeland Horticulture Ltd53.5016</t>
+  </si>
+  <si>
+    <t>George Whittaker &amp; Sons (Knutsford) Limited53.26558</t>
+  </si>
+  <si>
+    <t>Greener Composting52.65658</t>
+  </si>
+  <si>
+    <t>Jack Moody Recycling 252.42737</t>
+  </si>
+  <si>
+    <t>James Heyes &amp; Sons53.48498</t>
+  </si>
+  <si>
+    <t>MEC Recycling53.16068</t>
+  </si>
+  <si>
+    <t>Material Change Composting Limited52.69838</t>
+  </si>
+  <si>
+    <t>SED Services Ltd53.50341</t>
+  </si>
+  <si>
+    <t>Veolia UK Ltd 352.6562266</t>
+  </si>
+  <si>
+    <t>Veolia UK Ltd 453.08038713</t>
+  </si>
+  <si>
+    <t>SUEZ Environment 252.4614199</t>
+  </si>
+  <si>
+    <t>Tamar Organics T/A Biogen 151.4035273</t>
+  </si>
+  <si>
+    <t>Tamar Organics T/A Biogen 251.72269825</t>
+  </si>
+  <si>
+    <t>Veolia ES (UK) Ltd51.5559918</t>
+  </si>
+  <si>
+    <t>The Greener Gardening Company Ltd53.47081</t>
+  </si>
+  <si>
+    <t>Jack Moody Recycling52.6137405</t>
+  </si>
+  <si>
+    <t>Willen Biogas Ltd51.6905</t>
+  </si>
+  <si>
+    <t>New Earth Solutions (West) Limited t/a Mid-UK Recycling52.78656</t>
+  </si>
+  <si>
+    <t>Land Network (Gainsborough) Limited53.3739599</t>
+  </si>
+  <si>
+    <t>Fife Resource Solutions56.0959338</t>
+  </si>
+  <si>
+    <t>Scott Bros Environmental Services Ltd54.5852547</t>
+  </si>
+  <si>
+    <t>SED Services Ltd53.52633</t>
+  </si>
+  <si>
+    <t>Durham County Council54.7226347</t>
+  </si>
+  <si>
+    <t>Friction Energy51.4101</t>
+  </si>
+  <si>
+    <t>John Cooper Recycling Ltd53.70721</t>
+  </si>
+  <si>
+    <t>Levenseat Ltd55.77816</t>
+  </si>
+  <si>
+    <t>Biowise Ltd53.11278</t>
+  </si>
+  <si>
+    <t>Jack Moody Ltd52.6573059</t>
+  </si>
+  <si>
+    <t>Severn Trent Green Power51.70461</t>
+  </si>
+  <si>
+    <t>THE FIRM OF A H TUCKER55.79174</t>
+  </si>
+  <si>
+    <t>GTP 3 Data Centre</t>
   </si>
 </sst>
 </file>
@@ -434,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -453,10 +696,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>17500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -464,10 +707,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>13000</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -475,10 +718,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>278</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>18615</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -486,10 +729,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="C5">
-        <v>71428.571</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -497,10 +740,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>36000</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -508,21 +751,21 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>60000</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>82</v>
+      <c r="B8" t="s">
+        <v>101</v>
       </c>
       <c r="C8">
-        <v>20000</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -530,10 +773,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="C9">
-        <v>20000</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -541,10 +784,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>199</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>71428.571</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -552,21 +795,21 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>10675</v>
+        <v>11610</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>49</v>
+      <c r="B12" t="s">
+        <v>101</v>
       </c>
       <c r="C12">
-        <v>20000</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -574,10 +817,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>3995.7143</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -585,10 +828,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="C14">
-        <v>20000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -596,10 +839,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>71428.571</v>
+        <v>10350</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -607,10 +850,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="C16">
-        <v>12500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -618,10 +861,10 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>22000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -629,10 +872,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>71428.571</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -640,10 +883,890 @@
         <v>20</v>
       </c>
       <c r="B19">
+        <v>28</v>
+      </c>
+      <c r="C19">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>60</v>
+      </c>
+      <c r="C20">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>60</v>
+      </c>
+      <c r="C21">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>72</v>
+      </c>
+      <c r="C22">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32">
+        <v>60</v>
+      </c>
+      <c r="C32">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+      <c r="C39">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40">
+        <v>72</v>
+      </c>
+      <c r="C40">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41">
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>48</v>
       </c>
-      <c r="C19">
-        <v>11428.571</v>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51">
+        <v>72</v>
+      </c>
+      <c r="C51">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+      <c r="C59">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61">
+        <v>9</v>
+      </c>
+      <c r="C61">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+      <c r="C63">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64">
+        <v>28</v>
+      </c>
+      <c r="C64">
+        <v>2811.4286</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65">
+        <v>60</v>
+      </c>
+      <c r="C65">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66">
+        <v>60</v>
+      </c>
+      <c r="C66">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68">
+        <v>5</v>
+      </c>
+      <c r="C68">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69">
+        <v>28</v>
+      </c>
+      <c r="C69">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70">
+        <v>60</v>
+      </c>
+      <c r="C70">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+      <c r="C71">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" t="s">
+        <v>101</v>
+      </c>
+      <c r="C72">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74">
+        <v>5</v>
+      </c>
+      <c r="C74">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75">
+        <v>60</v>
+      </c>
+      <c r="C75">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76">
+        <v>72</v>
+      </c>
+      <c r="C76">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+      <c r="C77">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79">
+        <v>60</v>
+      </c>
+      <c r="C79">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83">
+        <v>9</v>
+      </c>
+      <c r="C83">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84">
+        <v>5</v>
+      </c>
+      <c r="C84">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C85">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86">
+        <v>9</v>
+      </c>
+      <c r="C86">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87">
+        <v>72</v>
+      </c>
+      <c r="C87">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88">
+        <v>60</v>
+      </c>
+      <c r="C88">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89">
+        <v>28</v>
+      </c>
+      <c r="C89">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91">
+        <v>5</v>
+      </c>
+      <c r="C91">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93">
+        <v>9</v>
+      </c>
+      <c r="C93">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
+      </c>
+      <c r="C94">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95">
+        <v>28</v>
+      </c>
+      <c r="C95">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96">
+        <v>5</v>
+      </c>
+      <c r="C96">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" t="s">
+        <v>101</v>
+      </c>
+      <c r="C97">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98">
+        <v>9</v>
+      </c>
+      <c r="C98">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99">
+        <v>28</v>
+      </c>
+      <c r="C99">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
